--- a/Employee_Reports_wi52/Chalana Ishan Dishanayake Dishanayake Pathiranage Q0569.xlsx
+++ b/Employee_Reports_wi52/Chalana Ishan Dishanayake Dishanayake Pathiranage Q0569.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1301,11 +1301,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1351,11 +1351,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-168</v>
+        <v>-176</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1400,11 +1400,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1449,11 +1449,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-366</v>
+        <v>-374</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1486,11 +1486,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-366</v>
+        <v>-374</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1523,11 +1523,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-168</v>
+        <v>-176</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1572,11 +1572,11 @@
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-182</v>
+        <v>-190</v>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -1621,11 +1621,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1670,11 +1670,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1719,11 +1719,11 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -1768,11 +1768,11 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -1805,11 +1805,11 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -1842,11 +1842,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1879,11 +1879,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1928,11 +1928,11 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -1977,11 +1977,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2014,11 +2014,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2063,11 +2063,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2100,11 +2100,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
